--- a/data/industry/CFM/DDR.xlsx
+++ b/data/industry/CFM/DDR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59EAA5DD-C3BC-4CA4-A2CD-A7FC79C776F4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00FD56B8-901E-4FCF-9559-84EDAB332854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="673" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" tabRatio="673" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DDR4 16Gb 3200" sheetId="1" r:id="rId1"/>
@@ -28,12 +28,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -341,6 +344,12 @@
                 <c:pt idx="33">
                   <c:v>46105</c:v>
                 </c:pt>
+                <c:pt idx="34">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46119</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -450,6 +459,12 @@
                   <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="33">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="35">
                   <c:v>50</c:v>
                 </c:pt>
               </c:numCache>
@@ -588,6 +603,12 @@
                 <c:pt idx="33">
                   <c:v>46105</c:v>
                 </c:pt>
+                <c:pt idx="34">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46119</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -697,6 +718,12 @@
                   <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="33">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="35">
                   <c:v>15</c:v>
                 </c:pt>
               </c:numCache>
@@ -835,6 +862,12 @@
                 <c:pt idx="33">
                   <c:v>46105</c:v>
                 </c:pt>
+                <c:pt idx="34">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46119</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -944,6 +977,12 @@
                   <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="33">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="35">
                   <c:v>15</c:v>
                 </c:pt>
               </c:numCache>
@@ -1082,6 +1121,12 @@
                 <c:pt idx="33">
                   <c:v>46105</c:v>
                 </c:pt>
+                <c:pt idx="34">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46119</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1191,6 +1236,12 @@
                   <c:v>7.4</c:v>
                 </c:pt>
                 <c:pt idx="33">
+                  <c:v>7.4</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>7.4</c:v>
+                </c:pt>
+                <c:pt idx="35">
                   <c:v>7.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -1329,6 +1380,12 @@
                 <c:pt idx="33">
                   <c:v>46105</c:v>
                 </c:pt>
+                <c:pt idx="34">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46119</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1438,6 +1495,12 @@
                   <c:v>2.7</c:v>
                 </c:pt>
                 <c:pt idx="33">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="35">
                   <c:v>2.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -1576,6 +1639,12 @@
                 <c:pt idx="33">
                   <c:v>46105</c:v>
                 </c:pt>
+                <c:pt idx="34">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46119</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1685,6 +1754,12 @@
                   <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="33">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="35">
                   <c:v>36</c:v>
                 </c:pt>
               </c:numCache>
@@ -1825,6 +1900,12 @@
                 <c:pt idx="33">
                   <c:v>46105</c:v>
                 </c:pt>
+                <c:pt idx="34">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46119</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1934,6 +2015,15 @@
                   <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="33">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="36">
                   <c:v>30</c:v>
                 </c:pt>
               </c:numCache>
@@ -2074,6 +2164,12 @@
                 <c:pt idx="33">
                   <c:v>46105</c:v>
                 </c:pt>
+                <c:pt idx="34">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46119</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2184,6 +2280,12 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>23</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3255,7 +3357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
@@ -4072,6 +4174,52 @@
         <v>50</v>
       </c>
     </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="9">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="9">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="12">
+        <v>40</v>
+      </c>
+      <c r="F36" s="12">
+        <v>80</v>
+      </c>
+      <c r="G36" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="9">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="12">
+        <v>40</v>
+      </c>
+      <c r="F37" s="12">
+        <v>80</v>
+      </c>
+      <c r="G37" s="12">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4081,7 +4229,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ECE58E1-E673-4989-AE5A-B8686BAF4454}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
@@ -4898,6 +5046,52 @@
         <v>15</v>
       </c>
     </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="9">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="9">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="12">
+        <v>13.5</v>
+      </c>
+      <c r="F36" s="12">
+        <v>15.5</v>
+      </c>
+      <c r="G36" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="9">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="12">
+        <v>13.5</v>
+      </c>
+      <c r="F37" s="12">
+        <v>15.5</v>
+      </c>
+      <c r="G37" s="12">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4906,7 +5100,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E892F627-73C7-4D50-84EF-2BEC5382C9F2}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
@@ -5723,6 +5917,52 @@
         <v>15</v>
       </c>
     </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="9">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="9">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="12">
+        <v>11</v>
+      </c>
+      <c r="F36" s="12">
+        <v>25</v>
+      </c>
+      <c r="G36" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="9">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="12">
+        <v>11</v>
+      </c>
+      <c r="F37" s="12">
+        <v>25</v>
+      </c>
+      <c r="G37" s="12">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5731,7 +5971,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E98E7142-8EB2-4D50-8855-47B862F141C9}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
@@ -6548,6 +6788,52 @@
         <v>7.4</v>
       </c>
     </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="9">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="9">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="12">
+        <v>6.9</v>
+      </c>
+      <c r="F36" s="12">
+        <v>7.9</v>
+      </c>
+      <c r="G36" s="12">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="9">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="12">
+        <v>6.9</v>
+      </c>
+      <c r="F37" s="12">
+        <v>7.9</v>
+      </c>
+      <c r="G37" s="12">
+        <v>7.4</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6556,7 +6842,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3674D84-1184-43AD-82E1-AE4900944B12}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
@@ -7373,6 +7659,52 @@
         <v>2.7</v>
       </c>
     </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="9">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="9">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="12">
+        <v>2.4</v>
+      </c>
+      <c r="F36" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="G36" s="12">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="9">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="12">
+        <v>2.4</v>
+      </c>
+      <c r="F37" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="G37" s="12">
+        <v>2.7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7381,7 +7713,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADBDF414-6821-49E6-A1DF-C17838025248}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
@@ -8198,6 +8530,52 @@
         <v>36</v>
       </c>
     </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="9">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="9">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="12">
+        <v>32</v>
+      </c>
+      <c r="F36" s="12">
+        <v>40</v>
+      </c>
+      <c r="G36" s="12">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="9">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="12">
+        <v>32</v>
+      </c>
+      <c r="F37" s="12">
+        <v>40</v>
+      </c>
+      <c r="G37" s="12">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8206,7 +8584,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4E0312D-9566-49D8-B0D1-D78DB0764F8E}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
@@ -9023,6 +9401,75 @@
         <v>30</v>
       </c>
     </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="9">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="9">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="12">
+        <v>28</v>
+      </c>
+      <c r="F36" s="12">
+        <v>32</v>
+      </c>
+      <c r="G36" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="9">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="12">
+        <v>28</v>
+      </c>
+      <c r="F37" s="12">
+        <v>32</v>
+      </c>
+      <c r="G37" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="9">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="9">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="12">
+        <v>28</v>
+      </c>
+      <c r="F38" s="12">
+        <v>32</v>
+      </c>
+      <c r="G38" s="12">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9031,7 +9478,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6397CE70-E09B-4668-A71C-5388D3A6C3B5}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
@@ -9848,9 +10295,56 @@
         <v>26</v>
       </c>
     </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="9">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="9">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="16">
+        <v>21</v>
+      </c>
+      <c r="F36" s="16">
+        <v>24</v>
+      </c>
+      <c r="G36" s="16">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="9">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="9">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="16">
+        <v>21</v>
+      </c>
+      <c r="F37" s="16">
+        <v>24</v>
+      </c>
+      <c r="G37" s="16">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/data/industry/CFM/DDR.xlsx
+++ b/data/industry/CFM/DDR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00FD56B8-901E-4FCF-9559-84EDAB332854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324AB728-F0F2-47DF-BF4D-C53B766BF541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" tabRatio="673" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="673" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DDR4 16Gb 3200" sheetId="1" r:id="rId1"/>
@@ -28,15 +28,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -350,6 +347,12 @@
                 <c:pt idx="35">
                   <c:v>46119</c:v>
                 </c:pt>
+                <c:pt idx="36">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46133</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -465,6 +468,12 @@
                   <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="35">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="37">
                   <c:v>50</c:v>
                 </c:pt>
               </c:numCache>
@@ -609,6 +618,12 @@
                 <c:pt idx="35">
                   <c:v>46119</c:v>
                 </c:pt>
+                <c:pt idx="36">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46133</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -724,6 +739,12 @@
                   <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="35">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="37">
                   <c:v>15</c:v>
                 </c:pt>
               </c:numCache>
@@ -868,6 +889,12 @@
                 <c:pt idx="35">
                   <c:v>46119</c:v>
                 </c:pt>
+                <c:pt idx="36">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46133</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -983,6 +1010,12 @@
                   <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="35">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="37">
                   <c:v>15</c:v>
                 </c:pt>
               </c:numCache>
@@ -1127,6 +1160,12 @@
                 <c:pt idx="35">
                   <c:v>46119</c:v>
                 </c:pt>
+                <c:pt idx="36">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46133</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1242,6 +1281,12 @@
                   <c:v>7.4</c:v>
                 </c:pt>
                 <c:pt idx="35">
+                  <c:v>7.4</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>7.4</c:v>
+                </c:pt>
+                <c:pt idx="37">
                   <c:v>7.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -1386,6 +1431,12 @@
                 <c:pt idx="35">
                   <c:v>46119</c:v>
                 </c:pt>
+                <c:pt idx="36">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46133</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1501,6 +1552,12 @@
                   <c:v>2.7</c:v>
                 </c:pt>
                 <c:pt idx="35">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="37">
                   <c:v>2.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -1645,6 +1702,12 @@
                 <c:pt idx="35">
                   <c:v>46119</c:v>
                 </c:pt>
+                <c:pt idx="36">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46133</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1760,6 +1823,12 @@
                   <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="35">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="37">
                   <c:v>36</c:v>
                 </c:pt>
               </c:numCache>
@@ -1906,6 +1975,12 @@
                 <c:pt idx="35">
                   <c:v>46119</c:v>
                 </c:pt>
+                <c:pt idx="36">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46133</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2024,6 +2099,12 @@
                   <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="36">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="38">
                   <c:v>30</c:v>
                 </c:pt>
               </c:numCache>
@@ -2170,6 +2251,12 @@
                 <c:pt idx="35">
                   <c:v>46119</c:v>
                 </c:pt>
+                <c:pt idx="36">
+                  <c:v>46126</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46133</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2286,6 +2373,12 @@
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>22</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2458,6 +2551,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2465,7 +2559,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3357,15 +3450,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -4217,6 +4310,52 @@
         <v>80</v>
       </c>
       <c r="G37" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="9">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="9">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="12">
+        <v>40</v>
+      </c>
+      <c r="F38" s="12">
+        <v>70</v>
+      </c>
+      <c r="G38" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="9">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="9">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="12">
+        <v>40</v>
+      </c>
+      <c r="F39" s="12">
+        <v>70</v>
+      </c>
+      <c r="G39" s="12">
         <v>50</v>
       </c>
     </row>
@@ -4229,15 +4368,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ECE58E1-E673-4989-AE5A-B8686BAF4454}">
-  <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -5089,6 +5228,52 @@
         <v>15.5</v>
       </c>
       <c r="G37" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="9">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="9">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="12">
+        <v>13.5</v>
+      </c>
+      <c r="F38" s="12">
+        <v>15.5</v>
+      </c>
+      <c r="G38" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="9">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="9">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="12">
+        <v>13.5</v>
+      </c>
+      <c r="F39" s="12">
+        <v>15.5</v>
+      </c>
+      <c r="G39" s="12">
         <v>15</v>
       </c>
     </row>
@@ -5100,15 +5285,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E892F627-73C7-4D50-84EF-2BEC5382C9F2}">
-  <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -5960,6 +6145,52 @@
         <v>25</v>
       </c>
       <c r="G37" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="9">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="9">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333332998</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="12">
+        <v>11</v>
+      </c>
+      <c r="F38" s="12">
+        <v>25</v>
+      </c>
+      <c r="G38" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="9">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="9">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333332898</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="12">
+        <v>11</v>
+      </c>
+      <c r="F39" s="12">
+        <v>25</v>
+      </c>
+      <c r="G39" s="12">
         <v>15</v>
       </c>
     </row>
@@ -5971,15 +6202,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E98E7142-8EB2-4D50-8855-47B862F141C9}">
-  <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -6831,6 +7062,52 @@
         <v>7.9</v>
       </c>
       <c r="G37" s="12">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="9">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="9">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="12">
+        <v>6.9</v>
+      </c>
+      <c r="F38" s="12">
+        <v>7.9</v>
+      </c>
+      <c r="G38" s="12">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="9">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="9">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="12">
+        <v>6.9</v>
+      </c>
+      <c r="F39" s="12">
+        <v>7.9</v>
+      </c>
+      <c r="G39" s="12">
         <v>7.4</v>
       </c>
     </row>
@@ -6842,15 +7119,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3674D84-1184-43AD-82E1-AE4900944B12}">
-  <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -7702,6 +7979,52 @@
         <v>3.2</v>
       </c>
       <c r="G37" s="12">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="9">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="9">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="12">
+        <v>2.4</v>
+      </c>
+      <c r="F38" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="G38" s="12">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="9">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="9">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="12">
+        <v>2.4</v>
+      </c>
+      <c r="F39" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="G39" s="12">
         <v>2.7</v>
       </c>
     </row>
@@ -7713,15 +8036,15 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADBDF414-6821-49E6-A1DF-C17838025248}">
-  <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -8573,6 +8896,52 @@
         <v>40</v>
       </c>
       <c r="G37" s="12">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="9">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="9">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="12">
+        <v>32</v>
+      </c>
+      <c r="F38" s="12">
+        <v>40</v>
+      </c>
+      <c r="G38" s="12">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="9">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="9">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="12">
+        <v>32</v>
+      </c>
+      <c r="F39" s="12">
+        <v>40</v>
+      </c>
+      <c r="G39" s="12">
         <v>36</v>
       </c>
     </row>
@@ -8584,15 +8953,15 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4E0312D-9566-49D8-B0D1-D78DB0764F8E}">
-  <dimension ref="A1:G38"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G40"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -9467,6 +9836,52 @@
         <v>32</v>
       </c>
       <c r="G38" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="9">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="9">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="12">
+        <v>28</v>
+      </c>
+      <c r="F39" s="12">
+        <v>32</v>
+      </c>
+      <c r="G39" s="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" s="9">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="9">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="12">
+        <v>28</v>
+      </c>
+      <c r="F40" s="12">
+        <v>32</v>
+      </c>
+      <c r="G40" s="12">
         <v>30</v>
       </c>
     </row>
@@ -9478,15 +9893,15 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6397CE70-E09B-4668-A71C-5388D3A6C3B5}">
-  <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="16"/>
-    <col min="7" max="7" width="11.25" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="16" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -10339,6 +10754,52 @@
       </c>
       <c r="G37" s="16">
         <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="9">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="9">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="16">
+        <v>20</v>
+      </c>
+      <c r="F38" s="16">
+        <v>23</v>
+      </c>
+      <c r="G38" s="16">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="9">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="9">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="16">
+        <v>20</v>
+      </c>
+      <c r="F39" s="16">
+        <v>23</v>
+      </c>
+      <c r="G39" s="16">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -10351,7 +10812,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{125E0383-8D21-4789-B003-A94DDDB82616}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/industry/CFM/DDR.xlsx
+++ b/data/industry/CFM/DDR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324AB728-F0F2-47DF-BF4D-C53B766BF541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{487751C1-704D-4311-8B6A-D323BC2B2CB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="673" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11430" yWindow="0" windowWidth="11700" windowHeight="14730" tabRatio="673" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DDR4 16Gb 3200" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -73,23 +73,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -102,7 +102,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -133,54 +133,54 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -198,7 +198,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -353,6 +353,27 @@
                 <c:pt idx="37">
                   <c:v>46133</c:v>
                 </c:pt>
+                <c:pt idx="38">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46154</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46161</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46175</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46182</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -474,6 +495,27 @@
                   <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="37">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="44">
                   <c:v>50</c:v>
                 </c:pt>
               </c:numCache>
@@ -624,6 +666,27 @@
                 <c:pt idx="37">
                   <c:v>46133</c:v>
                 </c:pt>
+                <c:pt idx="38">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46154</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46161</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46175</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46182</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -745,6 +808,27 @@
                   <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="37">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="44">
                   <c:v>15</c:v>
                 </c:pt>
               </c:numCache>
@@ -895,6 +979,27 @@
                 <c:pt idx="37">
                   <c:v>46133</c:v>
                 </c:pt>
+                <c:pt idx="38">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46154</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46161</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46175</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46182</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1017,6 +1122,27 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>18</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1166,6 +1292,27 @@
                 <c:pt idx="37">
                   <c:v>46133</c:v>
                 </c:pt>
+                <c:pt idx="38">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46154</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46161</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46175</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46182</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1287,6 +1434,27 @@
                   <c:v>7.4</c:v>
                 </c:pt>
                 <c:pt idx="37">
+                  <c:v>7.4</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>7.4</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>7.4</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>7.4</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>7.4</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>7.4</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>7.4</c:v>
+                </c:pt>
+                <c:pt idx="44">
                   <c:v>7.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -1437,6 +1605,27 @@
                 <c:pt idx="37">
                   <c:v>46133</c:v>
                 </c:pt>
+                <c:pt idx="38">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46154</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46161</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46175</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46182</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1558,6 +1747,27 @@
                   <c:v>2.7</c:v>
                 </c:pt>
                 <c:pt idx="37">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="44">
                   <c:v>2.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -1708,6 +1918,27 @@
                 <c:pt idx="37">
                   <c:v>46133</c:v>
                 </c:pt>
+                <c:pt idx="38">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46154</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46161</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46175</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46182</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1830,6 +2061,27 @@
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>40</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1981,6 +2233,27 @@
                 <c:pt idx="37">
                   <c:v>46133</c:v>
                 </c:pt>
+                <c:pt idx="38">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46154</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46161</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46175</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46182</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2106,6 +2379,24 @@
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>35</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2257,6 +2548,27 @@
                 <c:pt idx="37">
                   <c:v>46133</c:v>
                 </c:pt>
+                <c:pt idx="38">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46154</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46161</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46175</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46182</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2378,6 +2690,27 @@
                   <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="37">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="44">
                   <c:v>22</c:v>
                 </c:pt>
               </c:numCache>
@@ -3450,19 +3783,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G46"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7265625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1796875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3485,7 +3818,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -3508,7 +3841,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -3531,7 +3864,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -3554,7 +3887,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -3577,7 +3910,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -3600,7 +3933,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -3623,7 +3956,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -3646,7 +3979,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -3669,7 +4002,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -3692,7 +4025,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -3715,7 +4048,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -3738,7 +4071,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -3761,7 +4094,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -3784,7 +4117,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -3807,7 +4140,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -3830,7 +4163,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -3853,7 +4186,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -3876,7 +4209,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -3899,7 +4232,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -3922,7 +4255,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -3945,7 +4278,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -3968,7 +4301,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -3991,7 +4324,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -4014,7 +4347,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -4037,7 +4370,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="9">
         <v>46035</v>
       </c>
@@ -4060,7 +4393,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="9">
         <v>46042</v>
       </c>
@@ -4083,7 +4416,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="9">
         <v>46049</v>
       </c>
@@ -4106,7 +4439,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="9">
         <v>46056</v>
       </c>
@@ -4129,7 +4462,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="9">
         <v>46063</v>
       </c>
@@ -4152,7 +4485,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="9">
         <v>46077</v>
       </c>
@@ -4175,7 +4508,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="9">
         <v>46084</v>
       </c>
@@ -4198,7 +4531,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="9">
         <v>46091</v>
       </c>
@@ -4221,7 +4554,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="9">
         <v>46098</v>
       </c>
@@ -4244,7 +4577,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="9">
         <v>46105</v>
       </c>
@@ -4267,7 +4600,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="9">
         <v>46112</v>
       </c>
@@ -4290,7 +4623,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="9">
         <v>46119</v>
       </c>
@@ -4313,7 +4646,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="9">
         <v>46126</v>
       </c>
@@ -4336,7 +4669,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="9">
         <v>46133</v>
       </c>
@@ -4356,6 +4689,167 @@
         <v>70</v>
       </c>
       <c r="G39" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="9">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="9">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="12">
+        <v>40</v>
+      </c>
+      <c r="F40" s="12">
+        <v>70</v>
+      </c>
+      <c r="G40" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="9">
+        <v>46147</v>
+      </c>
+      <c r="B41" s="9">
+        <v>46147</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="12">
+        <v>40</v>
+      </c>
+      <c r="F41" s="12">
+        <v>70</v>
+      </c>
+      <c r="G41" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="9">
+        <v>46154</v>
+      </c>
+      <c r="B42" s="9">
+        <v>46154</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="12">
+        <v>40</v>
+      </c>
+      <c r="F42" s="12">
+        <v>70</v>
+      </c>
+      <c r="G42" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="9">
+        <v>46161</v>
+      </c>
+      <c r="B43" s="9">
+        <v>46161</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="12">
+        <v>40</v>
+      </c>
+      <c r="F43" s="12">
+        <v>70</v>
+      </c>
+      <c r="G43" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="9">
+        <v>46168</v>
+      </c>
+      <c r="B44" s="9">
+        <v>46168</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="12">
+        <v>40</v>
+      </c>
+      <c r="F44" s="12">
+        <v>70</v>
+      </c>
+      <c r="G44" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="9">
+        <v>46175</v>
+      </c>
+      <c r="B45" s="9">
+        <v>46175</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="12">
+        <v>40</v>
+      </c>
+      <c r="F45" s="12">
+        <v>70</v>
+      </c>
+      <c r="G45" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="9">
+        <v>46182</v>
+      </c>
+      <c r="B46" s="9">
+        <v>46182</v>
+      </c>
+      <c r="C46" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="12">
+        <v>40</v>
+      </c>
+      <c r="F46" s="12">
+        <v>70</v>
+      </c>
+      <c r="G46" s="12">
         <v>50</v>
       </c>
     </row>
@@ -4368,19 +4862,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ECE58E1-E673-4989-AE5A-B8686BAF4454}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G46"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7265625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1796875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4403,7 +4897,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -4426,7 +4920,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -4449,7 +4943,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -4472,7 +4966,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -4495,7 +4989,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -4518,7 +5012,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -4541,7 +5035,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -4564,7 +5058,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -4587,7 +5081,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -4610,7 +5104,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -4633,7 +5127,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -4656,7 +5150,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -4679,7 +5173,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -4702,7 +5196,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -4725,7 +5219,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -4748,7 +5242,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -4771,7 +5265,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -4794,7 +5288,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -4817,7 +5311,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -4840,7 +5334,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -4863,7 +5357,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -4886,7 +5380,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -4909,7 +5403,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -4932,7 +5426,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -4955,7 +5449,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="9">
         <v>46035</v>
       </c>
@@ -4978,7 +5472,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="9">
         <v>46042</v>
       </c>
@@ -5001,7 +5495,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="9">
         <v>46049</v>
       </c>
@@ -5024,7 +5518,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="9">
         <v>46056</v>
       </c>
@@ -5047,7 +5541,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="9">
         <v>46063</v>
       </c>
@@ -5070,7 +5564,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="9">
         <v>46077</v>
       </c>
@@ -5093,7 +5587,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="9">
         <v>46084</v>
       </c>
@@ -5116,7 +5610,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="9">
         <v>46091</v>
       </c>
@@ -5139,7 +5633,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="9">
         <v>46098</v>
       </c>
@@ -5162,7 +5656,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="9">
         <v>46105</v>
       </c>
@@ -5185,7 +5679,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="9">
         <v>46112</v>
       </c>
@@ -5208,7 +5702,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="9">
         <v>46119</v>
       </c>
@@ -5231,7 +5725,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="9">
         <v>46126</v>
       </c>
@@ -5254,7 +5748,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="9">
         <v>46133</v>
       </c>
@@ -5274,6 +5768,167 @@
         <v>15.5</v>
       </c>
       <c r="G39" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="9">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="9">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="12">
+        <v>13.5</v>
+      </c>
+      <c r="F40" s="12">
+        <v>15.5</v>
+      </c>
+      <c r="G40" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="9">
+        <v>46147</v>
+      </c>
+      <c r="B41" s="9">
+        <v>46147</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="12">
+        <v>13.5</v>
+      </c>
+      <c r="F41" s="12">
+        <v>15.5</v>
+      </c>
+      <c r="G41" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="9">
+        <v>46154</v>
+      </c>
+      <c r="B42" s="9">
+        <v>46154</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="12">
+        <v>13.5</v>
+      </c>
+      <c r="F42" s="12">
+        <v>15.5</v>
+      </c>
+      <c r="G42" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="9">
+        <v>46161</v>
+      </c>
+      <c r="B43" s="9">
+        <v>46161</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="12">
+        <v>13.5</v>
+      </c>
+      <c r="F43" s="12">
+        <v>15.5</v>
+      </c>
+      <c r="G43" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="9">
+        <v>46168</v>
+      </c>
+      <c r="B44" s="9">
+        <v>46168</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="12">
+        <v>13.5</v>
+      </c>
+      <c r="F44" s="12">
+        <v>15.5</v>
+      </c>
+      <c r="G44" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="9">
+        <v>46175</v>
+      </c>
+      <c r="B45" s="9">
+        <v>46175</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="12">
+        <v>13.5</v>
+      </c>
+      <c r="F45" s="12">
+        <v>15.5</v>
+      </c>
+      <c r="G45" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="9">
+        <v>46182</v>
+      </c>
+      <c r="B46" s="9">
+        <v>46182</v>
+      </c>
+      <c r="C46" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="12">
+        <v>13.5</v>
+      </c>
+      <c r="F46" s="12">
+        <v>15.5</v>
+      </c>
+      <c r="G46" s="12">
         <v>15</v>
       </c>
     </row>
@@ -5285,19 +5940,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E892F627-73C7-4D50-84EF-2BEC5382C9F2}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G46"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7265625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1796875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5320,7 +5975,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -5343,7 +5998,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -5366,7 +6021,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -5389,7 +6044,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -5412,7 +6067,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -5435,7 +6090,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -5458,7 +6113,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -5481,7 +6136,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -5504,7 +6159,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -5527,7 +6182,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -5550,7 +6205,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -5573,7 +6228,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -5596,7 +6251,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -5619,7 +6274,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -5642,7 +6297,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -5665,7 +6320,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -5688,7 +6343,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -5711,7 +6366,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -5734,7 +6389,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -5757,7 +6412,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -5780,7 +6435,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -5803,7 +6458,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -5826,7 +6481,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -5849,7 +6504,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -5872,7 +6527,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="9">
         <v>46035</v>
       </c>
@@ -5895,7 +6550,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="9">
         <v>46042</v>
       </c>
@@ -5918,7 +6573,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="9">
         <v>46049</v>
       </c>
@@ -5941,7 +6596,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="9">
         <v>46056</v>
       </c>
@@ -5964,7 +6619,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="9">
         <v>46063</v>
       </c>
@@ -5987,7 +6642,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="9">
         <v>46077</v>
       </c>
@@ -6010,7 +6665,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="9">
         <v>46084</v>
       </c>
@@ -6033,7 +6688,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="9">
         <v>46091</v>
       </c>
@@ -6056,7 +6711,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="9">
         <v>46098</v>
       </c>
@@ -6079,7 +6734,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="9">
         <v>46105</v>
       </c>
@@ -6102,7 +6757,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="9">
         <v>46112</v>
       </c>
@@ -6125,7 +6780,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="9">
         <v>46119</v>
       </c>
@@ -6148,7 +6803,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="9">
         <v>46126</v>
       </c>
@@ -6171,7 +6826,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="9">
         <v>46133</v>
       </c>
@@ -6192,6 +6847,167 @@
       </c>
       <c r="G39" s="12">
         <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="9">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="9">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333332599</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="12">
+        <v>11</v>
+      </c>
+      <c r="F40" s="12">
+        <v>25</v>
+      </c>
+      <c r="G40" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="9">
+        <v>46147</v>
+      </c>
+      <c r="B41" s="9">
+        <v>46147</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333332399</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="12">
+        <v>16</v>
+      </c>
+      <c r="F41" s="12">
+        <v>28</v>
+      </c>
+      <c r="G41" s="12">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="9">
+        <v>46154</v>
+      </c>
+      <c r="B42" s="9">
+        <v>46154</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333332199</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="12">
+        <v>16</v>
+      </c>
+      <c r="F42" s="12">
+        <v>28</v>
+      </c>
+      <c r="G42" s="12">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="9">
+        <v>46161</v>
+      </c>
+      <c r="B43" s="9">
+        <v>46161</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333331999</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="12">
+        <v>16</v>
+      </c>
+      <c r="F43" s="12">
+        <v>28</v>
+      </c>
+      <c r="G43" s="12">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="9">
+        <v>46168</v>
+      </c>
+      <c r="B44" s="9">
+        <v>46168</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333331799</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="12">
+        <v>16</v>
+      </c>
+      <c r="F44" s="12">
+        <v>28</v>
+      </c>
+      <c r="G44" s="12">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="9">
+        <v>46175</v>
+      </c>
+      <c r="B45" s="9">
+        <v>46175</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.458333333333316</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="12">
+        <v>16</v>
+      </c>
+      <c r="F45" s="12">
+        <v>28</v>
+      </c>
+      <c r="G45" s="12">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="9">
+        <v>46182</v>
+      </c>
+      <c r="B46" s="9">
+        <v>46182</v>
+      </c>
+      <c r="C46" s="7">
+        <v>0.458333333333314</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="12">
+        <v>16</v>
+      </c>
+      <c r="F46" s="12">
+        <v>28</v>
+      </c>
+      <c r="G46" s="12">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -6202,19 +7018,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E98E7142-8EB2-4D50-8855-47B862F141C9}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G46"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7265625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1796875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6237,7 +7053,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -6260,7 +7076,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -6283,7 +7099,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -6306,7 +7122,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -6329,7 +7145,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -6352,7 +7168,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -6375,7 +7191,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -6398,7 +7214,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -6421,7 +7237,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -6444,7 +7260,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -6467,7 +7283,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -6490,7 +7306,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -6513,7 +7329,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -6536,7 +7352,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -6559,7 +7375,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -6582,7 +7398,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -6605,7 +7421,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -6628,7 +7444,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -6651,7 +7467,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -6674,7 +7490,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -6697,7 +7513,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -6720,7 +7536,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -6743,7 +7559,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -6766,7 +7582,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -6789,7 +7605,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="9">
         <v>46035</v>
       </c>
@@ -6812,7 +7628,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="9">
         <v>46042</v>
       </c>
@@ -6835,7 +7651,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="9">
         <v>46049</v>
       </c>
@@ -6858,7 +7674,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="9">
         <v>46056</v>
       </c>
@@ -6881,7 +7697,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="9">
         <v>46063</v>
       </c>
@@ -6904,7 +7720,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="9">
         <v>46077</v>
       </c>
@@ -6927,7 +7743,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="9">
         <v>46084</v>
       </c>
@@ -6950,7 +7766,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="9">
         <v>46091</v>
       </c>
@@ -6973,7 +7789,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="9">
         <v>46098</v>
       </c>
@@ -6996,7 +7812,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="9">
         <v>46105</v>
       </c>
@@ -7019,7 +7835,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="9">
         <v>46112</v>
       </c>
@@ -7042,7 +7858,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="9">
         <v>46119</v>
       </c>
@@ -7065,7 +7881,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="9">
         <v>46126</v>
       </c>
@@ -7088,7 +7904,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="9">
         <v>46133</v>
       </c>
@@ -7108,6 +7924,167 @@
         <v>7.9</v>
       </c>
       <c r="G39" s="12">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="9">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="9">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="12">
+        <v>6.9</v>
+      </c>
+      <c r="F40" s="12">
+        <v>7.9</v>
+      </c>
+      <c r="G40" s="12">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="9">
+        <v>46147</v>
+      </c>
+      <c r="B41" s="9">
+        <v>46147</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="12">
+        <v>6.9</v>
+      </c>
+      <c r="F41" s="12">
+        <v>7.9</v>
+      </c>
+      <c r="G41" s="12">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="9">
+        <v>46154</v>
+      </c>
+      <c r="B42" s="9">
+        <v>46154</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="12">
+        <v>6.9</v>
+      </c>
+      <c r="F42" s="12">
+        <v>7.9</v>
+      </c>
+      <c r="G42" s="12">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="9">
+        <v>46161</v>
+      </c>
+      <c r="B43" s="9">
+        <v>46161</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="12">
+        <v>6.9</v>
+      </c>
+      <c r="F43" s="12">
+        <v>7.9</v>
+      </c>
+      <c r="G43" s="12">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="9">
+        <v>46168</v>
+      </c>
+      <c r="B44" s="9">
+        <v>46168</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="12">
+        <v>6.9</v>
+      </c>
+      <c r="F44" s="12">
+        <v>7.9</v>
+      </c>
+      <c r="G44" s="12">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="9">
+        <v>46175</v>
+      </c>
+      <c r="B45" s="9">
+        <v>46175</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="12">
+        <v>6.9</v>
+      </c>
+      <c r="F45" s="12">
+        <v>7.9</v>
+      </c>
+      <c r="G45" s="12">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="9">
+        <v>46182</v>
+      </c>
+      <c r="B46" s="9">
+        <v>46182</v>
+      </c>
+      <c r="C46" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="12">
+        <v>6.9</v>
+      </c>
+      <c r="F46" s="12">
+        <v>7.9</v>
+      </c>
+      <c r="G46" s="12">
         <v>7.4</v>
       </c>
     </row>
@@ -7119,19 +8096,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3674D84-1184-43AD-82E1-AE4900944B12}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G46"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7265625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1796875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7154,7 +8131,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -7177,7 +8154,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -7200,7 +8177,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -7223,7 +8200,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -7246,7 +8223,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -7269,7 +8246,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -7292,7 +8269,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -7315,7 +8292,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -7338,7 +8315,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -7361,7 +8338,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -7384,7 +8361,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -7407,7 +8384,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -7430,7 +8407,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -7453,7 +8430,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -7476,7 +8453,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -7499,7 +8476,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -7522,7 +8499,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -7545,7 +8522,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -7568,7 +8545,7 @@
         <v>1.72</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -7591,7 +8568,7 @@
         <v>1.72</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -7614,7 +8591,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -7637,7 +8614,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -7660,7 +8637,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -7683,7 +8660,7 @@
         <v>1.85</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -7706,7 +8683,7 @@
         <v>1.85</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="9">
         <v>46035</v>
       </c>
@@ -7729,7 +8706,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="9">
         <v>46042</v>
       </c>
@@ -7752,7 +8729,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="9">
         <v>46049</v>
       </c>
@@ -7775,7 +8752,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="9">
         <v>46056</v>
       </c>
@@ -7798,7 +8775,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="9">
         <v>46063</v>
       </c>
@@ -7821,7 +8798,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="9">
         <v>46077</v>
       </c>
@@ -7844,7 +8821,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="9">
         <v>46084</v>
       </c>
@@ -7867,7 +8844,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="9">
         <v>46091</v>
       </c>
@@ -7890,7 +8867,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="9">
         <v>46098</v>
       </c>
@@ -7913,7 +8890,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="9">
         <v>46105</v>
       </c>
@@ -7936,7 +8913,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="9">
         <v>46112</v>
       </c>
@@ -7959,7 +8936,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="9">
         <v>46119</v>
       </c>
@@ -7982,7 +8959,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="9">
         <v>46126</v>
       </c>
@@ -8005,7 +8982,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="9">
         <v>46133</v>
       </c>
@@ -8025,6 +9002,167 @@
         <v>3.2</v>
       </c>
       <c r="G39" s="12">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="9">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="9">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="12">
+        <v>2.4</v>
+      </c>
+      <c r="F40" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="G40" s="12">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="9">
+        <v>46147</v>
+      </c>
+      <c r="B41" s="9">
+        <v>46147</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="12">
+        <v>2.4</v>
+      </c>
+      <c r="F41" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="G41" s="12">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="9">
+        <v>46154</v>
+      </c>
+      <c r="B42" s="9">
+        <v>46154</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="12">
+        <v>2.4</v>
+      </c>
+      <c r="F42" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="G42" s="12">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="9">
+        <v>46161</v>
+      </c>
+      <c r="B43" s="9">
+        <v>46161</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="12">
+        <v>2.4</v>
+      </c>
+      <c r="F43" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="G43" s="12">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="9">
+        <v>46168</v>
+      </c>
+      <c r="B44" s="9">
+        <v>46168</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="12">
+        <v>2.4</v>
+      </c>
+      <c r="F44" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="G44" s="12">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="9">
+        <v>46175</v>
+      </c>
+      <c r="B45" s="9">
+        <v>46175</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="12">
+        <v>2.4</v>
+      </c>
+      <c r="F45" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="G45" s="12">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="9">
+        <v>46182</v>
+      </c>
+      <c r="B46" s="9">
+        <v>46182</v>
+      </c>
+      <c r="C46" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="12">
+        <v>2.4</v>
+      </c>
+      <c r="F46" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="G46" s="12">
         <v>2.7</v>
       </c>
     </row>
@@ -8036,19 +9174,19 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADBDF414-6821-49E6-A1DF-C17838025248}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G46"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7265625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1796875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8071,7 +9209,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -8094,7 +9232,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -8117,7 +9255,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -8140,7 +9278,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -8163,7 +9301,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -8186,7 +9324,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -8209,7 +9347,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -8232,7 +9370,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -8255,7 +9393,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -8278,7 +9416,7 @@
         <v>7.95</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -8301,7 +9439,7 @@
         <v>7.95</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -8324,7 +9462,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -8347,7 +9485,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -8370,7 +9508,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -8393,7 +9531,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -8416,7 +9554,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -8439,7 +9577,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -8462,7 +9600,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -8485,7 +9623,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -8508,7 +9646,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -8531,7 +9669,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -8554,7 +9692,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -8577,7 +9715,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -8600,7 +9738,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -8623,7 +9761,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="9">
         <v>46035</v>
       </c>
@@ -8646,7 +9784,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="9">
         <v>46042</v>
       </c>
@@ -8669,7 +9807,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="9">
         <v>46049</v>
       </c>
@@ -8692,7 +9830,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="9">
         <v>46056</v>
       </c>
@@ -8715,7 +9853,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="9">
         <v>46063</v>
       </c>
@@ -8738,7 +9876,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="9">
         <v>46077</v>
       </c>
@@ -8761,7 +9899,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="9">
         <v>46084</v>
       </c>
@@ -8784,7 +9922,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="9">
         <v>46091</v>
       </c>
@@ -8807,7 +9945,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="9">
         <v>46098</v>
       </c>
@@ -8830,7 +9968,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="9">
         <v>46105</v>
       </c>
@@ -8853,7 +9991,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="9">
         <v>46112</v>
       </c>
@@ -8876,7 +10014,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="9">
         <v>46119</v>
       </c>
@@ -8899,7 +10037,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="9">
         <v>46126</v>
       </c>
@@ -8922,7 +10060,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="9">
         <v>46133</v>
       </c>
@@ -8943,6 +10081,167 @@
       </c>
       <c r="G39" s="12">
         <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="9">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="9">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="12">
+        <v>32</v>
+      </c>
+      <c r="F40" s="12">
+        <v>40</v>
+      </c>
+      <c r="G40" s="12">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="9">
+        <v>46147</v>
+      </c>
+      <c r="B41" s="9">
+        <v>46147</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="12">
+        <v>36</v>
+      </c>
+      <c r="F41" s="12">
+        <v>44</v>
+      </c>
+      <c r="G41" s="12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="9">
+        <v>46154</v>
+      </c>
+      <c r="B42" s="9">
+        <v>46154</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="12">
+        <v>36</v>
+      </c>
+      <c r="F42" s="12">
+        <v>44</v>
+      </c>
+      <c r="G42" s="12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="9">
+        <v>46161</v>
+      </c>
+      <c r="B43" s="9">
+        <v>46161</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="12">
+        <v>36</v>
+      </c>
+      <c r="F43" s="12">
+        <v>44</v>
+      </c>
+      <c r="G43" s="12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="9">
+        <v>46168</v>
+      </c>
+      <c r="B44" s="9">
+        <v>46168</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="12">
+        <v>36</v>
+      </c>
+      <c r="F44" s="12">
+        <v>44</v>
+      </c>
+      <c r="G44" s="12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="9">
+        <v>46175</v>
+      </c>
+      <c r="B45" s="9">
+        <v>46175</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="12">
+        <v>36</v>
+      </c>
+      <c r="F45" s="12">
+        <v>44</v>
+      </c>
+      <c r="G45" s="12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="9">
+        <v>46182</v>
+      </c>
+      <c r="B46" s="9">
+        <v>46182</v>
+      </c>
+      <c r="C46" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="12">
+        <v>36</v>
+      </c>
+      <c r="F46" s="12">
+        <v>44</v>
+      </c>
+      <c r="G46" s="12">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -8953,19 +10252,19 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4E0312D-9566-49D8-B0D1-D78DB0764F8E}">
-  <dimension ref="A1:G40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G46"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7265625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1796875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8988,7 +10287,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -9011,7 +10310,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -9034,7 +10333,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -9057,7 +10356,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -9080,7 +10379,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -9103,7 +10402,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -9126,7 +10425,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -9149,7 +10448,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -9172,7 +10471,7 @@
         <v>4.95</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -9195,7 +10494,7 @@
         <v>5.05</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -9218,7 +10517,7 @@
         <v>5.25</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -9241,7 +10540,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -9264,7 +10563,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -9287,7 +10586,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -9310,7 +10609,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -9333,7 +10632,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -9356,7 +10655,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -9379,7 +10678,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -9402,7 +10701,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -9425,7 +10724,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -9448,7 +10747,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -9471,7 +10770,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -9494,7 +10793,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -9517,7 +10816,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -9540,7 +10839,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="9">
         <v>46035</v>
       </c>
@@ -9563,7 +10862,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="9">
         <v>46042</v>
       </c>
@@ -9586,7 +10885,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="9">
         <v>46049</v>
       </c>
@@ -9609,7 +10908,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="9">
         <v>46056</v>
       </c>
@@ -9632,7 +10931,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="9">
         <v>46063</v>
       </c>
@@ -9655,7 +10954,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="9">
         <v>46077</v>
       </c>
@@ -9678,7 +10977,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="9">
         <v>46084</v>
       </c>
@@ -9701,7 +11000,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="9">
         <v>46091</v>
       </c>
@@ -9724,7 +11023,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="9">
         <v>46098</v>
       </c>
@@ -9747,7 +11046,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="9">
         <v>46105</v>
       </c>
@@ -9770,7 +11069,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="9">
         <v>46112</v>
       </c>
@@ -9793,7 +11092,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="9">
         <v>46119</v>
       </c>
@@ -9816,7 +11115,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="9">
         <v>46126</v>
       </c>
@@ -9839,7 +11138,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="9">
         <v>46133</v>
       </c>
@@ -9862,7 +11161,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7">
       <c r="A40" s="9">
         <v>46140</v>
       </c>
@@ -9883,6 +11182,144 @@
       </c>
       <c r="G40" s="12">
         <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="9">
+        <v>46147</v>
+      </c>
+      <c r="B41" s="9">
+        <v>46147</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="12">
+        <v>33</v>
+      </c>
+      <c r="F41" s="12">
+        <v>37</v>
+      </c>
+      <c r="G41" s="12">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="9">
+        <v>46154</v>
+      </c>
+      <c r="B42" s="9">
+        <v>46154</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="12">
+        <v>33</v>
+      </c>
+      <c r="F42" s="12">
+        <v>37</v>
+      </c>
+      <c r="G42" s="12">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="9">
+        <v>46161</v>
+      </c>
+      <c r="B43" s="9">
+        <v>46161</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="12">
+        <v>33</v>
+      </c>
+      <c r="F43" s="12">
+        <v>37</v>
+      </c>
+      <c r="G43" s="12">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="9">
+        <v>46168</v>
+      </c>
+      <c r="B44" s="9">
+        <v>46168</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="12">
+        <v>33</v>
+      </c>
+      <c r="F44" s="12">
+        <v>37</v>
+      </c>
+      <c r="G44" s="12">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="9">
+        <v>46175</v>
+      </c>
+      <c r="B45" s="9">
+        <v>46175</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="12">
+        <v>33</v>
+      </c>
+      <c r="F45" s="12">
+        <v>37</v>
+      </c>
+      <c r="G45" s="12">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="9">
+        <v>46182</v>
+      </c>
+      <c r="B46" s="9">
+        <v>46182</v>
+      </c>
+      <c r="C46" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="12">
+        <v>33</v>
+      </c>
+      <c r="F46" s="12">
+        <v>37</v>
+      </c>
+      <c r="G46" s="12">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -9893,19 +11330,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6397CE70-E09B-4668-A71C-5388D3A6C3B5}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G46"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7265625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="16"/>
-    <col min="7" max="7" width="11.19921875" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1796875" style="16" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9928,7 +11365,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -9951,7 +11388,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -9974,7 +11411,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -9997,7 +11434,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -10020,7 +11457,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -10043,7 +11480,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -10066,7 +11503,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -10089,7 +11526,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -10112,7 +11549,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -10135,7 +11572,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -10158,7 +11595,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -10181,7 +11618,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -10204,7 +11641,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -10227,7 +11664,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -10250,7 +11687,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -10273,7 +11710,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -10296,7 +11733,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -10319,7 +11756,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -10342,7 +11779,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -10365,7 +11802,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -10388,7 +11825,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -10411,7 +11848,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -10434,7 +11871,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -10457,7 +11894,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -10480,7 +11917,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="9">
         <v>46035</v>
       </c>
@@ -10503,7 +11940,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="9">
         <v>46042</v>
       </c>
@@ -10526,7 +11963,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="9">
         <v>46049</v>
       </c>
@@ -10549,7 +11986,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="9">
         <v>46056</v>
       </c>
@@ -10572,7 +12009,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="9">
         <v>46063</v>
       </c>
@@ -10595,7 +12032,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="9">
         <v>46077</v>
       </c>
@@ -10618,7 +12055,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="9">
         <v>46084</v>
       </c>
@@ -10641,7 +12078,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="9">
         <v>46091</v>
       </c>
@@ -10664,7 +12101,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="9">
         <v>46098</v>
       </c>
@@ -10687,7 +12124,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="9">
         <v>46105</v>
       </c>
@@ -10710,7 +12147,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="9">
         <v>46112</v>
       </c>
@@ -10733,7 +12170,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="9">
         <v>46119</v>
       </c>
@@ -10756,7 +12193,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="9">
         <v>46126</v>
       </c>
@@ -10779,7 +12216,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="9">
         <v>46133</v>
       </c>
@@ -10799,6 +12236,167 @@
         <v>23</v>
       </c>
       <c r="G39" s="16">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="9">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="9">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="16">
+        <v>20</v>
+      </c>
+      <c r="F40" s="16">
+        <v>23</v>
+      </c>
+      <c r="G40" s="16">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="9">
+        <v>46147</v>
+      </c>
+      <c r="B41" s="9">
+        <v>46147</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="16">
+        <v>20</v>
+      </c>
+      <c r="F41" s="16">
+        <v>23</v>
+      </c>
+      <c r="G41" s="16">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="9">
+        <v>46154</v>
+      </c>
+      <c r="B42" s="9">
+        <v>46154</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="16">
+        <v>20</v>
+      </c>
+      <c r="F42" s="16">
+        <v>23</v>
+      </c>
+      <c r="G42" s="16">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="9">
+        <v>46161</v>
+      </c>
+      <c r="B43" s="9">
+        <v>46161</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="16">
+        <v>20</v>
+      </c>
+      <c r="F43" s="16">
+        <v>23</v>
+      </c>
+      <c r="G43" s="16">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="9">
+        <v>46168</v>
+      </c>
+      <c r="B44" s="9">
+        <v>46168</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="16">
+        <v>20</v>
+      </c>
+      <c r="F44" s="16">
+        <v>23</v>
+      </c>
+      <c r="G44" s="16">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="9">
+        <v>46175</v>
+      </c>
+      <c r="B45" s="9">
+        <v>46175</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="16">
+        <v>20</v>
+      </c>
+      <c r="F45" s="16">
+        <v>23</v>
+      </c>
+      <c r="G45" s="16">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="9">
+        <v>46182</v>
+      </c>
+      <c r="B46" s="9">
+        <v>46182</v>
+      </c>
+      <c r="C46" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="16">
+        <v>20</v>
+      </c>
+      <c r="F46" s="16">
+        <v>23</v>
+      </c>
+      <c r="G46" s="16">
         <v>22</v>
       </c>
     </row>
@@ -10812,7 +12410,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{125E0383-8D21-4789-B003-A94DDDB82616}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/industry/CFM/DDR.xlsx
+++ b/data/industry/CFM/DDR.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{487751C1-704D-4311-8B6A-D323BC2B2CB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B9CFB9-4589-4914-8E18-E4C781234908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11430" yWindow="0" windowWidth="11700" windowHeight="14730" tabRatio="673" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="673" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DDR4 16Gb 3200" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -179,8 +179,8 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -198,7 +198,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -374,6 +374,15 @@
                 <c:pt idx="44">
                   <c:v>46182</c:v>
                 </c:pt>
+                <c:pt idx="45">
+                  <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46196</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46203</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -516,6 +525,15 @@
                   <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="44">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="47">
                   <c:v>50</c:v>
                 </c:pt>
               </c:numCache>
@@ -687,6 +705,15 @@
                 <c:pt idx="44">
                   <c:v>46182</c:v>
                 </c:pt>
+                <c:pt idx="45">
+                  <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46196</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46203</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -829,6 +856,15 @@
                   <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="44">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="47">
                   <c:v>15</c:v>
                 </c:pt>
               </c:numCache>
@@ -1000,6 +1036,15 @@
                 <c:pt idx="44">
                   <c:v>46182</c:v>
                 </c:pt>
+                <c:pt idx="45">
+                  <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46196</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46203</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1142,6 +1187,15 @@
                   <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="44">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="47">
                   <c:v>18</c:v>
                 </c:pt>
               </c:numCache>
@@ -1313,6 +1367,15 @@
                 <c:pt idx="44">
                   <c:v>46182</c:v>
                 </c:pt>
+                <c:pt idx="45">
+                  <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46196</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46203</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1455,6 +1518,15 @@
                   <c:v>7.4</c:v>
                 </c:pt>
                 <c:pt idx="44">
+                  <c:v>7.4</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>7.4</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>7.4</c:v>
+                </c:pt>
+                <c:pt idx="47">
                   <c:v>7.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -1626,6 +1698,15 @@
                 <c:pt idx="44">
                   <c:v>46182</c:v>
                 </c:pt>
+                <c:pt idx="45">
+                  <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46196</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46203</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1768,6 +1849,15 @@
                   <c:v>2.7</c:v>
                 </c:pt>
                 <c:pt idx="44">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="47">
                   <c:v>2.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -1939,6 +2029,15 @@
                 <c:pt idx="44">
                   <c:v>46182</c:v>
                 </c:pt>
+                <c:pt idx="45">
+                  <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46196</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46203</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2081,6 +2180,15 @@
                   <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="44">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="47">
                   <c:v>40</c:v>
                 </c:pt>
               </c:numCache>
@@ -2254,6 +2362,15 @@
                 <c:pt idx="44">
                   <c:v>46182</c:v>
                 </c:pt>
+                <c:pt idx="45">
+                  <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46196</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46203</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2396,6 +2513,15 @@
                   <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="44">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="47">
                   <c:v>35</c:v>
                 </c:pt>
               </c:numCache>
@@ -2569,6 +2695,15 @@
                 <c:pt idx="44">
                   <c:v>46182</c:v>
                 </c:pt>
+                <c:pt idx="45">
+                  <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46196</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46203</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2711,6 +2846,15 @@
                   <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="44">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="47">
                   <c:v>22</c:v>
                 </c:pt>
               </c:numCache>
@@ -3783,15 +3927,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:G49"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.7265625" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1796875" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.1796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -4850,6 +4994,75 @@
         <v>70</v>
       </c>
       <c r="G46" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="9">
+        <v>46189</v>
+      </c>
+      <c r="B47" s="9">
+        <v>46189</v>
+      </c>
+      <c r="C47" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="12">
+        <v>40</v>
+      </c>
+      <c r="F47" s="12">
+        <v>70</v>
+      </c>
+      <c r="G47" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="9">
+        <v>46196</v>
+      </c>
+      <c r="B48" s="9">
+        <v>46196</v>
+      </c>
+      <c r="C48" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="12">
+        <v>40</v>
+      </c>
+      <c r="F48" s="12">
+        <v>70</v>
+      </c>
+      <c r="G48" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="9">
+        <v>46203</v>
+      </c>
+      <c r="B49" s="9">
+        <v>46203</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="12">
+        <v>40</v>
+      </c>
+      <c r="F49" s="12">
+        <v>70</v>
+      </c>
+      <c r="G49" s="12">
         <v>50</v>
       </c>
     </row>
@@ -4862,15 +5075,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ECE58E1-E673-4989-AE5A-B8686BAF4454}">
-  <dimension ref="A1:G46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:G49"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.7265625" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1796875" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.1796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -5929,6 +6142,75 @@
         <v>15.5</v>
       </c>
       <c r="G46" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="9">
+        <v>46189</v>
+      </c>
+      <c r="B47" s="9">
+        <v>46189</v>
+      </c>
+      <c r="C47" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="12">
+        <v>13.5</v>
+      </c>
+      <c r="F47" s="12">
+        <v>15.5</v>
+      </c>
+      <c r="G47" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="9">
+        <v>46196</v>
+      </c>
+      <c r="B48" s="9">
+        <v>46196</v>
+      </c>
+      <c r="C48" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="12">
+        <v>13.5</v>
+      </c>
+      <c r="F48" s="12">
+        <v>15.5</v>
+      </c>
+      <c r="G48" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="9">
+        <v>46203</v>
+      </c>
+      <c r="B49" s="9">
+        <v>46203</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="12">
+        <v>13.5</v>
+      </c>
+      <c r="F49" s="12">
+        <v>15.5</v>
+      </c>
+      <c r="G49" s="12">
         <v>15</v>
       </c>
     </row>
@@ -5940,15 +6222,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E892F627-73C7-4D50-84EF-2BEC5382C9F2}">
-  <dimension ref="A1:G46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:G49"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.7265625" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1796875" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.1796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -7007,6 +7289,75 @@
         <v>28</v>
       </c>
       <c r="G46" s="12">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="9">
+        <v>46189</v>
+      </c>
+      <c r="B47" s="9">
+        <v>46189</v>
+      </c>
+      <c r="C47" s="7">
+        <v>0.458333333333312</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="12">
+        <v>16</v>
+      </c>
+      <c r="F47" s="12">
+        <v>28</v>
+      </c>
+      <c r="G47" s="12">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="9">
+        <v>46196</v>
+      </c>
+      <c r="B48" s="9">
+        <v>46196</v>
+      </c>
+      <c r="C48" s="7">
+        <v>0.45833333333331</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="12">
+        <v>16</v>
+      </c>
+      <c r="F48" s="12">
+        <v>28</v>
+      </c>
+      <c r="G48" s="12">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="9">
+        <v>46203</v>
+      </c>
+      <c r="B49" s="9">
+        <v>46203</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.458333333333308</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="12">
+        <v>16</v>
+      </c>
+      <c r="F49" s="12">
+        <v>28</v>
+      </c>
+      <c r="G49" s="12">
         <v>18</v>
       </c>
     </row>
@@ -7018,15 +7369,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E98E7142-8EB2-4D50-8855-47B862F141C9}">
-  <dimension ref="A1:G46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:G49"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.7265625" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1796875" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.1796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -8085,6 +8436,75 @@
         <v>7.9</v>
       </c>
       <c r="G46" s="12">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="9">
+        <v>46189</v>
+      </c>
+      <c r="B47" s="9">
+        <v>46189</v>
+      </c>
+      <c r="C47" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="12">
+        <v>6.9</v>
+      </c>
+      <c r="F47" s="12">
+        <v>7.9</v>
+      </c>
+      <c r="G47" s="12">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="9">
+        <v>46196</v>
+      </c>
+      <c r="B48" s="9">
+        <v>46196</v>
+      </c>
+      <c r="C48" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="12">
+        <v>6.9</v>
+      </c>
+      <c r="F48" s="12">
+        <v>7.9</v>
+      </c>
+      <c r="G48" s="12">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="9">
+        <v>46203</v>
+      </c>
+      <c r="B49" s="9">
+        <v>46203</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="12">
+        <v>6.9</v>
+      </c>
+      <c r="F49" s="12">
+        <v>7.9</v>
+      </c>
+      <c r="G49" s="12">
         <v>7.4</v>
       </c>
     </row>
@@ -8096,15 +8516,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3674D84-1184-43AD-82E1-AE4900944B12}">
-  <dimension ref="A1:G46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:G49"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.7265625" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1796875" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.1796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -9163,6 +9583,75 @@
         <v>3.2</v>
       </c>
       <c r="G46" s="12">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="9">
+        <v>46189</v>
+      </c>
+      <c r="B47" s="9">
+        <v>46189</v>
+      </c>
+      <c r="C47" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="12">
+        <v>2.4</v>
+      </c>
+      <c r="F47" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="G47" s="12">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="9">
+        <v>46196</v>
+      </c>
+      <c r="B48" s="9">
+        <v>46196</v>
+      </c>
+      <c r="C48" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="12">
+        <v>2.4</v>
+      </c>
+      <c r="F48" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="G48" s="12">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="9">
+        <v>46203</v>
+      </c>
+      <c r="B49" s="9">
+        <v>46203</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="12">
+        <v>2.4</v>
+      </c>
+      <c r="F49" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="G49" s="12">
         <v>2.7</v>
       </c>
     </row>
@@ -9174,15 +9663,15 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADBDF414-6821-49E6-A1DF-C17838025248}">
-  <dimension ref="A1:G46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:G49"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.7265625" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1796875" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.1796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -10241,6 +10730,75 @@
         <v>44</v>
       </c>
       <c r="G46" s="12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="9">
+        <v>46189</v>
+      </c>
+      <c r="B47" s="9">
+        <v>46189</v>
+      </c>
+      <c r="C47" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="12">
+        <v>36</v>
+      </c>
+      <c r="F47" s="12">
+        <v>44</v>
+      </c>
+      <c r="G47" s="12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="9">
+        <v>46196</v>
+      </c>
+      <c r="B48" s="9">
+        <v>46196</v>
+      </c>
+      <c r="C48" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="12">
+        <v>36</v>
+      </c>
+      <c r="F48" s="12">
+        <v>44</v>
+      </c>
+      <c r="G48" s="12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="9">
+        <v>46203</v>
+      </c>
+      <c r="B49" s="9">
+        <v>46203</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="12">
+        <v>36</v>
+      </c>
+      <c r="F49" s="12">
+        <v>44</v>
+      </c>
+      <c r="G49" s="12">
         <v>40</v>
       </c>
     </row>
@@ -10252,15 +10810,15 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4E0312D-9566-49D8-B0D1-D78DB0764F8E}">
-  <dimension ref="A1:G46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:G49"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.7265625" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1796875" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.1796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -11319,6 +11877,75 @@
         <v>37</v>
       </c>
       <c r="G46" s="12">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="9">
+        <v>46189</v>
+      </c>
+      <c r="B47" s="9">
+        <v>46189</v>
+      </c>
+      <c r="C47" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="12">
+        <v>33</v>
+      </c>
+      <c r="F47" s="12">
+        <v>37</v>
+      </c>
+      <c r="G47" s="12">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="9">
+        <v>46196</v>
+      </c>
+      <c r="B48" s="9">
+        <v>46196</v>
+      </c>
+      <c r="C48" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="12">
+        <v>33</v>
+      </c>
+      <c r="F48" s="12">
+        <v>37</v>
+      </c>
+      <c r="G48" s="12">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="9">
+        <v>46203</v>
+      </c>
+      <c r="B49" s="9">
+        <v>46203</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="12">
+        <v>33</v>
+      </c>
+      <c r="F49" s="12">
+        <v>37</v>
+      </c>
+      <c r="G49" s="12">
         <v>35</v>
       </c>
     </row>
@@ -11330,15 +11957,15 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6397CE70-E09B-4668-A71C-5388D3A6C3B5}">
-  <dimension ref="A1:G46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:G49"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.7265625" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1796875" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="16"/>
-    <col min="7" max="7" width="11.1796875" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="16" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -12397,6 +13024,75 @@
         <v>23</v>
       </c>
       <c r="G46" s="16">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="9">
+        <v>46189</v>
+      </c>
+      <c r="B47" s="9">
+        <v>46189</v>
+      </c>
+      <c r="C47" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="16">
+        <v>20</v>
+      </c>
+      <c r="F47" s="16">
+        <v>23</v>
+      </c>
+      <c r="G47" s="16">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="9">
+        <v>46196</v>
+      </c>
+      <c r="B48" s="9">
+        <v>46196</v>
+      </c>
+      <c r="C48" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="16">
+        <v>20</v>
+      </c>
+      <c r="F48" s="16">
+        <v>23</v>
+      </c>
+      <c r="G48" s="16">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="9">
+        <v>46203</v>
+      </c>
+      <c r="B49" s="9">
+        <v>46203</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="16">
+        <v>20</v>
+      </c>
+      <c r="F49" s="16">
+        <v>23</v>
+      </c>
+      <c r="G49" s="16">
         <v>22</v>
       </c>
     </row>
@@ -12410,7 +13106,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{125E0383-8D21-4789-B003-A94DDDB82616}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
